--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -4,31 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="food" sheetId="1" r:id="rId1"/>
     <sheet name="boss_debuff" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -117,7 +104,7 @@
     <t>food_gold</t>
   </si>
   <si>
-    <t>街边小吃</t>
+    <t>美食</t>
   </si>
   <si>
     <t>普通美食：主要奖励金币。</t>
@@ -135,9 +122,6 @@
     <t>food_fragment</t>
   </si>
   <si>
-    <t>胃口扩张</t>
-  </si>
-  <si>
     <t>普通美食：主要奖励胃部碎片。</t>
   </si>
   <si>
@@ -150,9 +134,6 @@
     <t>food_passive</t>
   </si>
   <si>
-    <t>招牌菜试炼</t>
-  </si>
-  <si>
     <t>普通美食：主要奖励被动道具。</t>
   </si>
   <si>
@@ -165,9 +146,6 @@
     <t>food_active</t>
   </si>
   <si>
-    <t>秘制小物</t>
-  </si>
-  <si>
     <t>普通美食：主要奖励主动道具。</t>
   </si>
   <si>
@@ -180,9 +158,6 @@
     <t>food_dish</t>
   </si>
   <si>
-    <t>新菜试做</t>
-  </si>
-  <si>
     <t>普通美食：主要奖励菜品。</t>
   </si>
   <si>
@@ -195,7 +170,7 @@
     <t>food_hard_gold</t>
   </si>
   <si>
-    <t>重口硬菜</t>
+    <t>超级美食</t>
   </si>
   <si>
     <t>困难美食：主要奖励金币。</t>
@@ -210,9 +185,6 @@
     <t>food_hard_fragment</t>
   </si>
   <si>
-    <t>硬菜扩胃</t>
-  </si>
-  <si>
     <t>困难美食：主要奖励胃部碎片。</t>
   </si>
   <si>
@@ -222,9 +194,6 @@
     <t>food_hard_passive</t>
   </si>
   <si>
-    <t>名厨考验</t>
-  </si>
-  <si>
     <t>困难美食：主要奖励被动道具。</t>
   </si>
   <si>
@@ -234,9 +203,6 @@
     <t>food_hard_active</t>
   </si>
   <si>
-    <t>险中取巧</t>
-  </si>
-  <si>
     <t>困难美食：主要奖励主动道具。</t>
   </si>
   <si>
@@ -246,9 +212,6 @@
     <t>food_hard_dish</t>
   </si>
   <si>
-    <t>稀有菜谱</t>
-  </si>
-  <si>
     <t>困难美食：主要奖励菜品。</t>
   </si>
   <si>
@@ -258,7 +221,7 @@
     <t>food_boss</t>
   </si>
   <si>
-    <t>大胃王挑战</t>
+    <t>盛宴</t>
   </si>
   <si>
     <t>周末盛宴 Boss。</t>
@@ -489,7 +452,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1602,10 +1565,10 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1617,10 +1580,10 @@
         <v>31</v>
       </c>
       <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
         <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -1628,13 +1591,13 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1646,10 +1609,10 @@
         <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -1657,13 +1620,13 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1675,10 +1638,10 @@
         <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1686,13 +1649,13 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1704,10 +1667,10 @@
         <v>31</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1715,13 +1678,13 @@
     </row>
     <row r="9" spans="2:11">
       <c r="B9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1730,13 +1693,13 @@
         <v>1.2</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1744,13 +1707,13 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1759,13 +1722,13 @@
         <v>1.25</v>
       </c>
       <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
         <v>57</v>
-      </c>
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" t="s">
-        <v>62</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1773,13 +1736,13 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1788,13 +1751,13 @@
         <v>1.3</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1802,13 +1765,13 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1817,13 +1780,13 @@
         <v>1.25</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K12">
         <v>7</v>
@@ -1831,13 +1794,13 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -1846,13 +1809,13 @@
         <v>1.25</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K13">
         <v>8</v>
@@ -1860,13 +1823,13 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -1875,10 +1838,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1919,13 +1882,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1933,22 +1896,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1976,16 +1939,16 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1993,16 +1956,16 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2010,16 +1973,16 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2027,16 +1990,16 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2044,16 +2007,16 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2061,16 +2024,16 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2078,16 +2041,16 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2095,16 +2058,16 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2112,16 +2075,16 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2129,16 +2092,16 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -2146,16 +2109,16 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -2163,16 +2126,16 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2180,16 +2143,16 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2197,16 +2160,16 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2214,16 +2177,16 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -2231,16 +2194,16 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F19">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -77,7 +77,7 @@
     <t>奖励外观类型</t>
   </si>
   <si>
-    <t>奖励包ID(空=用当前周奖励包)</t>
+    <t>奖励包ID</t>
   </si>
   <si>
     <t>隐藏分加成</t>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>reward_food_boss</t>
   </si>
   <si>
     <t>modifier</t>
@@ -1843,6 +1846,9 @@
       <c r="I14" t="s">
         <v>71</v>
       </c>
+      <c r="J14" t="s">
+        <v>72</v>
+      </c>
       <c r="K14">
         <v>0</v>
       </c>
@@ -1882,13 +1888,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1896,22 +1902,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1939,16 +1945,16 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1956,16 +1962,16 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1973,16 +1979,16 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1990,16 +1996,16 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2007,16 +2013,16 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2024,16 +2030,16 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2041,16 +2047,16 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2058,16 +2064,16 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2075,16 +2081,16 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2092,16 +2098,16 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -2109,16 +2115,16 @@
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -2126,16 +2132,16 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2143,16 +2149,16 @@
     </row>
     <row r="16" spans="2:6">
       <c r="B16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2160,16 +2166,16 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2177,16 +2183,16 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -2194,16 +2200,16 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F19">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="food" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -32,22 +32,28 @@
     <t>isBoss</t>
   </si>
   <si>
-    <t>scoreProfileId</t>
-  </si>
-  <si>
-    <t>targetScoreMul</t>
-  </si>
-  <si>
-    <t>goldCurveId</t>
-  </si>
-  <si>
     <t>rewardKind</t>
   </si>
   <si>
     <t>rewardPackageId</t>
   </si>
   <si>
-    <t>hiddenScoreBonus</t>
+    <t>targetScoreHiddenOffset</t>
+  </si>
+  <si>
+    <t>dishHiddenOffset</t>
+  </si>
+  <si>
+    <t>passiveItemHiddenOffset</t>
+  </si>
+  <si>
+    <t>activeItemHiddenOffset</t>
+  </si>
+  <si>
+    <t>fragmentHiddenOffset</t>
+  </si>
+  <si>
+    <t>goldHiddenOffset</t>
   </si>
   <si>
     <t>##comment</t>
@@ -65,22 +71,28 @@
     <t>是否 Boss 战</t>
   </si>
   <si>
-    <t>目标分曲线(空=用当前周曲线)</t>
-  </si>
-  <si>
-    <t>普通/困难目标分倍率(Boss 用曲线 bossMul)</t>
-  </si>
-  <si>
-    <t>金币奖励曲线ID</t>
-  </si>
-  <si>
     <t>奖励外观类型</t>
   </si>
   <si>
     <t>奖励包ID</t>
   </si>
   <si>
-    <t>隐藏分加成</t>
+    <t>目标分隐藏分临时修正。</t>
+  </si>
+  <si>
+    <t>食物奖励隐藏分临时修正。</t>
+  </si>
+  <si>
+    <t>被动道具奖励隐藏分临时修正。</t>
+  </si>
+  <si>
+    <t>主动道具奖励隐藏分临时修正。</t>
+  </si>
+  <si>
+    <t>餐桌格子奖励隐藏分临时修正。</t>
+  </si>
+  <si>
+    <t>金币奖励隐藏分临时修正。</t>
   </si>
   <si>
     <t>##type</t>
@@ -92,12 +104,12 @@
     <t>bool</t>
   </si>
   <si>
+    <t>RewardKind</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
-    <t>RewardKind</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -110,9 +122,6 @@
     <t>普通美食：主要奖励金币。</t>
   </si>
   <si>
-    <t>gold_normal</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
@@ -176,9 +185,6 @@
     <t>困难美食：主要奖励金币。</t>
   </si>
   <si>
-    <t>gold_hard</t>
-  </si>
-  <si>
     <t>reward_food_hard_gold</t>
   </si>
   <si>
@@ -225,9 +231,6 @@
   </si>
   <si>
     <t>周末盛宴 Boss。</t>
-  </si>
-  <si>
-    <t>gold_boss</t>
   </si>
   <si>
     <t>None</t>
@@ -1063,8 +1066,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1411,446 +1417,562 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="21.0769230769231" customWidth="1"/>
-    <col min="3" max="3" width="16.3846153846154" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" customWidth="1"/>
-    <col min="5" max="5" width="13.5384615384615" customWidth="1"/>
-    <col min="6" max="6" width="32.6923076923077" customWidth="1"/>
-    <col min="7" max="7" width="46.2307692307692" customWidth="1"/>
-    <col min="8" max="8" width="17.9230769230769" customWidth="1"/>
-    <col min="9" max="9" width="19.2307692307692" customWidth="1"/>
-    <col min="10" max="10" width="33.0769230769231" customWidth="1"/>
-    <col min="11" max="11" width="18.7692307692308" customWidth="1"/>
-    <col min="12" max="12" width="12.7692307692308" customWidth="1"/>
-    <col min="13" max="13" width="15.1538461538462" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="21.0769230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3846153846154" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5384615384615" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.2307692307692" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.0769230769231" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.3076923076923" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.6923076923077" style="1" customWidth="1"/>
+    <col min="10" max="12" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.6923076923077" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J4" t="s">
+      <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" t="s">
+      <c r="D4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J5" t="s">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K5">
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>7</v>
+      </c>
+      <c r="J9" s="1">
+        <v>7</v>
+      </c>
+      <c r="K9" s="1">
+        <v>7</v>
+      </c>
+      <c r="L9" s="1">
+        <v>7</v>
+      </c>
+      <c r="M9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8</v>
+      </c>
+      <c r="J10" s="1">
+        <v>8</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>8</v>
+      </c>
+      <c r="M10" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1">
+        <v>9</v>
+      </c>
+      <c r="K11" s="1">
+        <v>9</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="G12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7</v>
+      </c>
+      <c r="K12" s="1">
+        <v>7</v>
+      </c>
+      <c r="L12" s="1">
+        <v>7</v>
+      </c>
+      <c r="M12" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1.2</v>
-      </c>
-      <c r="H9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" t="s">
+      <c r="G13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8</v>
+      </c>
+      <c r="K13" s="1">
+        <v>8</v>
+      </c>
+      <c r="L13" s="1">
+        <v>8</v>
+      </c>
+      <c r="M13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8</v>
+      </c>
+      <c r="J14" s="1">
+        <v>8</v>
+      </c>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>8</v>
+      </c>
+      <c r="M14" s="1">
         <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1.25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1.3</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1.25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1.25</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1865,353 +1987,354 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="21.0769230769231" customWidth="1"/>
-    <col min="3" max="3" width="16.3846153846154" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" customWidth="1"/>
-    <col min="5" max="5" width="13.5384615384615" customWidth="1"/>
-    <col min="6" max="6" width="32.6923076923077" customWidth="1"/>
-    <col min="7" max="7" width="46.2307692307692" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.0769230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3846153846154" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.7692307692308" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.4615384615385" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.6923076923077" style="1" customWidth="1"/>
+    <col min="7" max="7" width="46.2307692307692" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F4">
+      <c r="E4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F5">
+      <c r="E5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F6">
+      <c r="E6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F7">
+      <c r="E7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C8" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F8">
+      <c r="E8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F9">
+      <c r="E9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C10" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F10">
+      <c r="E10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F11">
+      <c r="E11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F12">
+      <c r="E12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F13">
+      <c r="E13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D14" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F14">
+      <c r="E14" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F15">
+      <c r="E15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F16">
+      <c r="E16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D17" t="s">
+      <c r="C17" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F17">
+      <c r="E17" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C18" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E18" t="s">
+      <c r="D18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F18">
+      <c r="E18" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E19" t="s">
+      <c r="D19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F19">
+      <c r="E19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="1">
         <v>1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="food" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="147">
   <si>
     <t>##var</t>
   </si>
@@ -110,9 +110,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>food_gold</t>
   </si>
   <si>
@@ -263,6 +260,9 @@
     <t>解锁条件(空=默认)</t>
   </si>
   <si>
+    <t>目标分隐藏分修正；加到 TargetScore 指数输入。</t>
+  </si>
+  <si>
     <t>debuff_indulgent</t>
   </si>
   <si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>feast_indulgent</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>debuff_kids_meal</t>
@@ -1066,8 +1069,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1420,558 +1426,558 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="21.0769230769231" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.3846153846154" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5384615384615" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.2307692307692" style="1" customWidth="1"/>
-    <col min="7" max="7" width="29.0769230769231" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.3076923076923" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.6923076923077" style="1" customWidth="1"/>
-    <col min="10" max="12" width="34.5384615384615" style="1" customWidth="1"/>
-    <col min="13" max="13" width="29.6923076923077" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.0769230769231" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.3846153846154" style="2" customWidth="1"/>
+    <col min="4" max="4" width="34.5384615384615" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.5384615384615" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.2307692307692" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.0769230769231" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.3076923076923" style="2" customWidth="1"/>
+    <col min="9" max="9" width="29.6923076923077" style="2" customWidth="1"/>
+    <col min="10" max="12" width="34.5384615384615" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.6923076923077" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K6" s="2">
         <v>2</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L6" s="2">
         <v>2</v>
       </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7</v>
+      </c>
+      <c r="J9" s="2">
+        <v>7</v>
+      </c>
+      <c r="K9" s="2">
+        <v>7</v>
+      </c>
+      <c r="L9" s="2">
+        <v>7</v>
+      </c>
+      <c r="M9" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2">
+        <v>8</v>
+      </c>
+      <c r="K10" s="2">
+        <v>8</v>
+      </c>
+      <c r="L10" s="2">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2</v>
-      </c>
-      <c r="L6" s="1">
-        <v>2</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="G11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>9</v>
+      </c>
+      <c r="L11" s="2">
+        <v>9</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="G12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7</v>
+      </c>
+      <c r="J12" s="2">
+        <v>7</v>
+      </c>
+      <c r="K12" s="2">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2">
+        <v>7</v>
+      </c>
+      <c r="M12" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="G13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="2">
         <v>0.5</v>
       </c>
-      <c r="I9" s="1">
-        <v>7</v>
-      </c>
-      <c r="J9" s="1">
-        <v>7</v>
-      </c>
-      <c r="K9" s="1">
-        <v>7</v>
-      </c>
-      <c r="L9" s="1">
-        <v>7</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="I13" s="2">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="1">
+    <row r="14" spans="2:13">
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
         <v>8</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J14" s="2">
         <v>8</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K14" s="2">
         <v>8</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L14" s="2">
         <v>8</v>
       </c>
-      <c r="M10" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="1">
-        <v>9</v>
-      </c>
-      <c r="J11" s="1">
-        <v>9</v>
-      </c>
-      <c r="K11" s="1">
-        <v>9</v>
-      </c>
-      <c r="L11" s="1">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="1">
-        <v>7</v>
-      </c>
-      <c r="J12" s="1">
-        <v>7</v>
-      </c>
-      <c r="K12" s="1">
-        <v>7</v>
-      </c>
-      <c r="L12" s="1">
-        <v>7</v>
-      </c>
-      <c r="M12" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="1">
-        <v>8</v>
-      </c>
-      <c r="J13" s="1">
-        <v>8</v>
-      </c>
-      <c r="K13" s="1">
-        <v>8</v>
-      </c>
-      <c r="L13" s="1">
-        <v>8</v>
-      </c>
-      <c r="M13" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>8</v>
-      </c>
-      <c r="J14" s="1">
-        <v>8</v>
-      </c>
-      <c r="K14" s="1">
-        <v>8</v>
-      </c>
-      <c r="L14" s="1">
-        <v>8</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="M14" s="2">
         <v>55</v>
       </c>
     </row>
@@ -1984,20 +1990,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.0769230769231" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.3846153846154" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="23.2307692307692" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1538461538462" style="1" customWidth="1"/>
     <col min="4" max="4" width="48.7692307692308" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.4615384615385" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.6923076923077" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46.2307692307692" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="10.3076923076923" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6153846153846" style="1" customWidth="1"/>
+    <col min="8" max="8" width="52.3846153846154" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2011,39 +2018,45 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -2065,8 +2078,11 @@
       <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="2:6">
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
       <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
@@ -2082,260 +2098,356 @@
       <c r="F4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
+      <c r="G4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
+      <c r="H5" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
+      <c r="G6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
+      <c r="G7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:6">
+      <c r="G8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
       <c r="B9" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
+      <c r="G9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="B10" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
+      <c r="G10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:6">
+      <c r="G11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
       <c r="B12" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="G12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
       <c r="B13" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
+      <c r="G13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
       <c r="B14" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:6">
+      <c r="G14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="2:6">
+      <c r="G15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
       <c r="B16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="G16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
+      <c r="G17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
       <c r="B18" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="G18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="food" sheetId="1" r:id="rId1"/>
@@ -269,7 +269,7 @@
     <t>放纵餐</t>
   </si>
   <si>
-    <t>获得一行与一列临时格子，美味度要求 x1.5。</t>
+    <t>获得一行与一列格子</t>
   </si>
   <si>
     <t>feast_indulgent</t>
@@ -284,7 +284,7 @@
     <t>儿童餐</t>
   </si>
   <si>
-    <t>失去一行与一列临时格子，美味度要求 x0.8。</t>
+    <t>失去一行与一列格子</t>
   </si>
   <si>
     <t>feast_kids_meal</t>
@@ -296,7 +296,7 @@
     <t>贪食餐</t>
   </si>
   <si>
-    <t>食谱中的食物翻倍，美味度要求 x1.1。</t>
+    <t>食谱中的食物翻倍</t>
   </si>
   <si>
     <t>feast_gluttony</t>
@@ -308,7 +308,7 @@
     <t>预制菜</t>
   </si>
   <si>
-    <t>本场调整食物基础次数为 0。</t>
+    <t>调整食物基础次数为 0</t>
   </si>
   <si>
     <t>feast_prefab_food</t>
@@ -320,7 +320,7 @@
     <t>Omakase</t>
   </si>
   <si>
-    <t>打乱各个食谱中的食物。</t>
+    <t>打乱各个食谱中的食物</t>
   </si>
   <si>
     <t>feast_omakase</t>
@@ -332,7 +332,7 @@
     <t>清淡餐</t>
   </si>
   <si>
-    <t>随机部分食物技能失效。</t>
+    <t>部分食物技能失效</t>
   </si>
   <si>
     <t>feast_light_meal</t>
@@ -344,7 +344,7 @@
     <t>斋饭</t>
   </si>
   <si>
-    <t>随机部分食物不参与分数汇总。</t>
+    <t>部分食物不会得分</t>
   </si>
   <si>
     <t>feast_vegan_meal</t>
@@ -356,7 +356,7 @@
     <t>霸王餐</t>
   </si>
   <si>
-    <t>每次上菜扣 5 金币，最低为 0。</t>
+    <t>每次上菜-5金币</t>
   </si>
   <si>
     <t>feast_dine_and_dash</t>
@@ -368,7 +368,7 @@
     <t>高级料理</t>
   </si>
   <si>
-    <t>所有食物基础分减半。</t>
+    <t>食物基础分减半</t>
   </si>
   <si>
     <t>feast_fine_dining</t>
@@ -380,7 +380,7 @@
     <t>素食</t>
   </si>
   <si>
-    <t>随机部分格子被禁用，无法上菜。</t>
+    <t>部分格子被禁用</t>
   </si>
   <si>
     <t>feast_vegetarian</t>
@@ -392,7 +392,7 @@
     <t>黑暗料理</t>
   </si>
   <si>
-    <t>上菜时倍率在 0.5 到 1.5 间随机。</t>
+    <t>食物的初始倍率随机化</t>
   </si>
   <si>
     <t>feast_dark_cuisine</t>
@@ -404,7 +404,7 @@
     <t>套餐</t>
   </si>
   <si>
-    <t>点击上菜会从本菜谱额外上一道菜。</t>
+    <t>上菜时，会从本菜谱额外上一道菜。</t>
   </si>
   <si>
     <t>feast_combo_meal</t>
@@ -428,7 +428,7 @@
     <t>开胃菜</t>
   </si>
   <si>
-    <t>前 3 个上的菜会消失。</t>
+    <t>前 3 个上的菜会消失</t>
   </si>
   <si>
     <t>feast_appetizer</t>
@@ -440,7 +440,7 @@
     <t>试吃</t>
   </si>
   <si>
-    <t>上菜倍率按 0.5 和 1.5 交替。</t>
+    <t>上菜时，食物倍率按0.5和1.5交替</t>
   </si>
   <si>
     <t>feast_tasting</t>
@@ -452,7 +452,7 @@
     <t>自助餐</t>
   </si>
   <si>
-    <t>必须上至少 10 个菜，否则没有分数。</t>
+    <t>必须上至少 10 个菜</t>
   </si>
   <si>
     <t>feast_buffet</t>
@@ -1069,11 +1069,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1426,558 +1423,558 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.0769230769231" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.3846153846154" style="2" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.5384615384615" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.2307692307692" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.0769230769231" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.3076923076923" style="2" customWidth="1"/>
-    <col min="9" max="9" width="29.6923076923077" style="2" customWidth="1"/>
-    <col min="10" max="12" width="34.5384615384615" style="2" customWidth="1"/>
-    <col min="13" max="13" width="29.6923076923077" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.0769230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3846153846154" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5384615384615" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.2307692307692" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.0769230769231" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.3076923076923" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.6923076923077" style="1" customWidth="1"/>
+    <col min="10" max="12" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29.6923076923077" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>2</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>2</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>2</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>0.5</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>7</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>7</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>7</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>0.5</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>8</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>8</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:13">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>0.5</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>9</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>9</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>9</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:13">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>0.5</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>7</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>7</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>7</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>7</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>0.5</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>8</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>8</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="1">
         <v>8</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>8</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
         <v>8</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>8</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>8</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1">
         <v>8</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="1">
         <v>55</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="food" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,8 @@
     <t>套餐</t>
   </si>
   <si>
-    <t>上菜时，会从本菜谱额外上一道菜。</t>
+    <t>上菜时
+会从本菜谱额外上一道菜。</t>
   </si>
   <si>
     <t>feast_combo_meal</t>
@@ -440,7 +441,8 @@
     <t>试吃</t>
   </si>
   <si>
-    <t>上菜时，食物倍率按0.5和1.5交替</t>
+    <t>上菜时
+食物倍率按0.5和1.5交替</t>
   </si>
   <si>
     <t>feast_tasting</t>
@@ -1069,10 +1071,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2332,14 +2337,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" ht="34" spans="2:8">
       <c r="B15" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -2401,14 +2406,14 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" ht="34" spans="2:8">
       <c r="B18" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E18" s="1" t="s">

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
@@ -1108,15 +1108,10 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>activeItemHiddenOffset</t>
+          <t>fragmentHiddenOffset</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>fragmentHiddenOffset</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>goldHiddenOffset</t>
         </is>
@@ -1175,15 +1170,10 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>主动道具奖励隐藏分临时修正。</t>
+          <t>餐桌格子奖励隐藏分临时修正。</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>餐桌格子奖励隐藏分临时修正。</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>金币奖励隐藏分临时修正。</t>
         </is>
@@ -1250,11 +1240,6 @@
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
@@ -1302,9 +1287,6 @@
       <c r="L4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
@@ -1350,9 +1332,6 @@
         <v>2</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1400,9 +1379,6 @@
         <v>2</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1450,9 +1426,6 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1500,9 +1473,6 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,9 +1520,6 @@
         <v>7</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1600,9 +1567,6 @@
         <v>8</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1650,9 +1614,6 @@
         <v>9</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1700,9 +1661,6 @@
         <v>7</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1750,9 +1708,6 @@
         <v>8</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="M13" s="1" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1800,9 +1755,6 @@
         <v>8</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" s="1" t="n">
         <v>55</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -170,7 +170,7 @@
     <t>food_boss</t>
   </si>
   <si>
-    <t>美食家评鉴</t>
+    <t>星级评鉴</t>
   </si>
   <si>
     <t>Feast</t>
@@ -1617,7 +1617,6 @@
       <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1638,7 +1637,6 @@
       <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1659,7 +1657,6 @@
       <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1680,7 +1677,6 @@
       <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1701,7 +1697,6 @@
       <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1722,7 +1717,6 @@
       <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
@@ -1743,7 +1737,6 @@
       <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1764,7 +1757,6 @@
       <c r="C11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
@@ -1785,7 +1777,6 @@
       <c r="C12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
         <v>40</v>
       </c>
@@ -1806,7 +1797,6 @@
       <c r="C13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
         <v>40</v>
       </c>
@@ -1827,7 +1817,6 @@
       <c r="C14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
         <v>52</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -113,22 +113,16 @@
     <t>reward_food_passive</t>
   </si>
   <si>
-    <t>food_active</t>
-  </si>
-  <si>
-    <t>ActiveItemGrant</t>
-  </si>
-  <si>
-    <t>reward_food_active</t>
-  </si>
-  <si>
-    <t>food_dish</t>
-  </si>
-  <si>
-    <t>DishChoice</t>
-  </si>
-  <si>
-    <t>reward_food_dish</t>
+    <t>food_active_strengthen</t>
+  </si>
+  <si>
+    <t>reward_food_active_strengthen</t>
+  </si>
+  <si>
+    <t>food_active_ajust</t>
+  </si>
+  <si>
+    <t>reward_active_ajust</t>
   </si>
   <si>
     <t>food_hard_gold</t>
@@ -155,16 +149,16 @@
     <t>reward_food_hard_passive</t>
   </si>
   <si>
-    <t>food_hard_active</t>
-  </si>
-  <si>
-    <t>reward_food_hard_active</t>
-  </si>
-  <si>
-    <t>food_hard_dish</t>
-  </si>
-  <si>
-    <t>reward_food_hard_dish</t>
+    <t>food_hard_active_strengthen</t>
+  </si>
+  <si>
+    <t>reward_food_hard_active_strengthen</t>
+  </si>
+  <si>
+    <t>food_hard_active_ajust</t>
+  </si>
+  <si>
+    <t>reward_food_hard_active_ajust</t>
   </si>
   <si>
     <t>food_boss</t>
@@ -549,7 +543,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -565,6 +559,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -885,7 +885,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -909,16 +909,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -927,89 +927,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1023,6 +1023,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1519,12 +1522,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.0769230769231" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.5384615384615" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.3846153846154" style="2" customWidth="1"/>
     <col min="4" max="4" width="34.5384615384615" style="2" customWidth="1"/>
     <col min="5" max="5" width="40.3076923076923" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.2307692307692" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.0769230769231" style="2" customWidth="1"/>
+    <col min="7" max="7" width="37.5384615384615" style="2" customWidth="1"/>
     <col min="8" max="8" width="27.3076923076923" style="2" customWidth="1"/>
     <col min="9" max="9" width="29.6923076923077" style="2" customWidth="1"/>
     <col min="10" max="12" width="34.5384615384615" style="2" customWidth="1"/>
@@ -1617,6 +1620,7 @@
       <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1637,6 +1641,7 @@
       <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1657,6 +1662,7 @@
       <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1670,61 +1676,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="2" t="s">
+    <row r="7" s="6" customFormat="1" spans="2:8">
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="6" customFormat="1" spans="2:8">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="H8" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2">
         <v>0.5</v>
@@ -1732,19 +1737,20 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H10" s="2">
         <v>0.5</v>
@@ -1752,79 +1758,78 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="2" t="s">
+    <row r="12" s="6" customFormat="1" spans="2:8">
+      <c r="B12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" s="6" customFormat="1" spans="2:8">
+      <c r="B13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="C13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="H13" s="6">
         <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1867,13 +1872,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -1884,25 +1889,25 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1934,16 +1939,16 @@
     <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -1955,16 +1960,16 @@
     <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1976,16 +1981,16 @@
     <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1997,16 +2002,16 @@
     <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -2018,16 +2023,16 @@
     <row r="8" spans="1:8">
       <c r="A8"/>
       <c r="B8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -2039,16 +2044,16 @@
     <row r="9" s="1" customFormat="1" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -2060,16 +2065,16 @@
     <row r="10" spans="1:8">
       <c r="A10"/>
       <c r="B10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F10" s="2">
         <v>1</v>
@@ -2081,16 +2086,16 @@
     <row r="11" spans="1:8">
       <c r="A11"/>
       <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
@@ -2102,16 +2107,16 @@
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
@@ -2123,16 +2128,16 @@
     <row r="13" spans="1:8">
       <c r="A13"/>
       <c r="B13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -2144,16 +2149,16 @@
     <row r="14" spans="1:8">
       <c r="A14"/>
       <c r="B14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -2165,16 +2170,16 @@
     <row r="15" s="1" customFormat="1" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -2186,16 +2191,16 @@
     <row r="16" spans="1:8">
       <c r="A16"/>
       <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
@@ -2207,16 +2212,16 @@
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17"/>
       <c r="B17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -2228,16 +2233,16 @@
     <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -2249,16 +2254,16 @@
     <row r="19" ht="34" spans="1:8">
       <c r="A19"/>
       <c r="B19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2270,16 +2275,16 @@
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20"/>
       <c r="B20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food" sheetId="1" r:id="R6ad9999326124673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss_debuff" sheetId="2" r:id="Rb389b31290674edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food" sheetId="1" r:id="R24a2587f6c164ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss_debuff" sheetId="2" r:id="Ra912a14f7450454b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -321,9 +321,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">碳水餐</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">出菜时有概率为馒头</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">feast_carb_meal</x:t>
@@ -506,7 +503,7 @@
       <x:name val="宋体"/>
     </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -681,6 +678,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -913,7 +915,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -930,6 +932,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1722,6 +1744,26 @@
     <x:col min="7" max="7" width="20.615385055541992" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="52.38461685180664" style="2" customWidth="1"/>
     <x:col min="9" max="16384" width="9" style="2" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="18" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1749,6 +1791,66 @@
       <x:c r="H1" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="I1" s="12" t="str">
+        <x:v>shapeLineCount</x:v>
+      </x:c>
+      <x:c r="J1" s="12" t="str">
+        <x:v>recipeCopyCount</x:v>
+      </x:c>
+      <x:c r="K1" s="12" t="str">
+        <x:v>foodDiscardLimit</x:v>
+      </x:c>
+      <x:c r="L1" s="12" t="str">
+        <x:v>recipeEntryDivisor</x:v>
+      </x:c>
+      <x:c r="M1" s="12" t="str">
+        <x:v>recipeEntryExtraCount</x:v>
+      </x:c>
+      <x:c r="N1" s="12" t="str">
+        <x:v>recipeEntryMinimumCount</x:v>
+      </x:c>
+      <x:c r="O1" s="12" t="str">
+        <x:v>goldCostPerBellServe</x:v>
+      </x:c>
+      <x:c r="P1" s="12" t="str">
+        <x:v>baseScoreMultiplier</x:v>
+      </x:c>
+      <x:c r="Q1" s="12" t="str">
+        <x:v>disabledCellDivisor</x:v>
+      </x:c>
+      <x:c r="R1" s="12" t="str">
+        <x:v>disabledCellExtraCount</x:v>
+      </x:c>
+      <x:c r="S1" s="12" t="str">
+        <x:v>insertDishId</x:v>
+      </x:c>
+      <x:c r="T1" s="12" t="str">
+        <x:v>insertDishWindowSize</x:v>
+      </x:c>
+      <x:c r="U1" s="12" t="str">
+        <x:v>insertDishCountPerWindow</x:v>
+      </x:c>
+      <x:c r="V1" s="12" t="str">
+        <x:v>randomServeMultiplierMin</x:v>
+      </x:c>
+      <x:c r="W1" s="12" t="str">
+        <x:v>randomServeMultiplierMax</x:v>
+      </x:c>
+      <x:c r="X1" s="12" t="str">
+        <x:v>randomServeMultiplierStep</x:v>
+      </x:c>
+      <x:c r="Y1" s="12" t="str">
+        <x:v>appetizerRemoveCount</x:v>
+      </x:c>
+      <x:c r="Z1" s="12" t="str">
+        <x:v>alternateServeMultiplierLow</x:v>
+      </x:c>
+      <x:c r="AA1" s="12" t="str">
+        <x:v>alternateServeMultiplierHigh</x:v>
+      </x:c>
+      <x:c r="AB1" s="12" t="str">
+        <x:v>minimumServesForScore</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
@@ -1775,6 +1877,66 @@
       <x:c r="H2" s="2" t="s">
         <x:v>57</x:v>
       </x:c>
+      <x:c r="I2" s="13" t="str">
+        <x:v>餐桌增减的行/列数量；放纵/暴食为增加，儿童/减脂为减少。</x:v>
+      </x:c>
+      <x:c r="J2" s="13" t="str">
+        <x:v>贪食餐为每个菜谱条目额外复制的份数。</x:v>
+      </x:c>
+      <x:c r="K2" s="13" t="str">
+        <x:v>本场食物废弃次数覆盖值；-1=不覆盖。</x:v>
+      </x:c>
+      <x:c r="L2" s="13" t="str">
+        <x:v>清淡餐/斋饭按菜谱数量计算受影响条目的除数；0=不启用。</x:v>
+      </x:c>
+      <x:c r="M2" s="13" t="str">
+        <x:v>清淡餐/斋饭受影响条目数量的额外加数。</x:v>
+      </x:c>
+      <x:c r="N2" s="13" t="str">
+        <x:v>清淡餐/斋饭受影响条目数量下限。</x:v>
+      </x:c>
+      <x:c r="O2" s="13" t="str">
+        <x:v>霸王餐每次成功摇铃出餐扣除金币。</x:v>
+      </x:c>
+      <x:c r="P2" s="13" t="str">
+        <x:v>高级料理的食物基础分倍率；1=不修正。</x:v>
+      </x:c>
+      <x:c r="Q2" s="13" t="str">
+        <x:v>素食按菜谱数量计算禁用格数量的除数；0=不启用。</x:v>
+      </x:c>
+      <x:c r="R2" s="13" t="str">
+        <x:v>素食禁用格数量的额外加数。</x:v>
+      </x:c>
+      <x:c r="S2" s="13" t="str">
+        <x:v>碳水餐插入出菜序列的独立菜品ID。</x:v>
+      </x:c>
+      <x:c r="T2" s="13" t="str">
+        <x:v>碳水餐随机窗口大小；例如5表示每5次为一组。</x:v>
+      </x:c>
+      <x:c r="U2" s="13" t="str">
+        <x:v>碳水餐每个窗口随机插入的菜品次数。</x:v>
+      </x:c>
+      <x:c r="V2" s="13" t="str">
+        <x:v>黑暗料理随机上菜倍率最小值。</x:v>
+      </x:c>
+      <x:c r="W2" s="13" t="str">
+        <x:v>黑暗料理随机上菜倍率最大值。</x:v>
+      </x:c>
+      <x:c r="X2" s="13" t="str">
+        <x:v>黑暗料理随机上菜倍率步长。</x:v>
+      </x:c>
+      <x:c r="Y2" s="13" t="str">
+        <x:v>开胃菜移除最先上桌的菜品数量。</x:v>
+      </x:c>
+      <x:c r="Z2" s="13" t="str">
+        <x:v>试吃奇数次上菜倍率。</x:v>
+      </x:c>
+      <x:c r="AA2" s="13" t="str">
+        <x:v>试吃偶数次上菜倍率。</x:v>
+      </x:c>
+      <x:c r="AB2" s="13" t="str">
+        <x:v>自助餐允许正常计分所需的最低上菜次数。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="s">
@@ -1800,6 +1962,66 @@
       </x:c>
       <x:c r="H3" s="2" t="s">
         <x:v>20</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="L3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="O3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="P3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="R3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="S3" s="13" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="T3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="U3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="V3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="W3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="X3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Y3" s="13" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Z3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AA3" s="13" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AB3" s="13" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1">
@@ -1822,6 +2044,64 @@
       <x:c r="H4" s="1">
         <x:v>0.5</x:v>
       </x:c>
+      <x:c r="I4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S4" s="14" t="str"/>
+      <x:c r="T4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA4" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="A5" s="3"/>
@@ -1843,6 +2123,64 @@
       <x:c r="H5" s="1">
         <x:v>0.5</x:v>
       </x:c>
+      <x:c r="I5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="14" t="str"/>
+      <x:c r="T5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA5" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1">
       <x:c r="A6" s="3"/>
@@ -1864,6 +2202,64 @@
       <x:c r="H6" s="1">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="I6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="14" t="str"/>
+      <x:c r="T6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
       <x:c r="A7" s="3"/>
@@ -1885,6 +2281,64 @@
       <x:c r="H7" s="1">
         <x:v>0.1</x:v>
       </x:c>
+      <x:c r="I7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="14" t="str"/>
+      <x:c r="T7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA7" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -1906,6 +2360,64 @@
       <x:c r="H8" s="2">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="14" t="str"/>
+      <x:c r="T8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA8" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1">
       <x:c r="A9" s="3"/>
@@ -1927,6 +2439,64 @@
       <x:c r="H9" s="1">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="14" t="str"/>
+      <x:c r="T9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA9" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
@@ -1948,6 +2518,64 @@
       <x:c r="H10" s="2">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L10" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="14" t="str"/>
+      <x:c r="T10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA10" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -1969,6 +2597,64 @@
       <x:c r="H11" s="2">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="14" t="str"/>
+      <x:c r="T11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="3"/>
@@ -1990,6 +2676,64 @@
       <x:c r="H12" s="1">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="14" t="str"/>
+      <x:c r="T12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA12" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
@@ -2011,6 +2755,64 @@
       <x:c r="H13" s="2">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="14" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="Q13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="14" t="str"/>
+      <x:c r="T13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA13" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB13" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
@@ -2032,6 +2834,64 @@
       <x:c r="H14" s="2">
         <x:v>0.35</x:v>
       </x:c>
+      <x:c r="I14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q14" s="14" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S14" s="14" t="str"/>
+      <x:c r="T14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA14" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="A15" s="3"/>
@@ -2041,122 +2901,472 @@
       <x:c r="C15" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="D15" s="1" t="str">
+        <x:v>每5次出菜随机插入1个馒头</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="14" t="str">
+        <x:v>mantou</x:v>
+      </x:c>
+      <x:c r="T15" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="U15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA15" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB15" s="14" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C16" s="2" t="s">
+      <x:c r="D16" s="2" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D16" s="2" t="s">
+      <x:c r="E16" s="2" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" s="14" t="str"/>
+      <x:c r="T16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V16" s="14" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="W16" s="14" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="X16" s="14" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="Y16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA16" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB16" s="14" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17"/>
       <x:c r="B17" s="2" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="C17" s="2" t="s">
+      <x:c r="D17" s="5" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D17" s="5" t="s">
+      <x:c r="E17" s="2" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="E17" s="2" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" s="14" t="str"/>
+      <x:c r="T17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y17" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA17" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB17" s="14" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="A18" s="3"/>
       <x:c r="B18" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="1">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="14" t="str"/>
+      <x:c r="T18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y18" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Z18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA18" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB18" s="14" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34">
       <x:c r="A19"/>
       <x:c r="B19" s="2" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="s">
+      <x:c r="D19" s="5" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="D19" s="5" t="s">
+      <x:c r="E19" s="2" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="F19" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="14" t="str"/>
+      <x:c r="T19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y19" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" s="14" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AA19" s="14" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="AB19" s="14" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
       <x:c r="A20"/>
       <x:c r="B20" s="2" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C20" s="2" t="s">
+      <x:c r="D20" s="5" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D20" s="5" t="s">
+      <x:c r="E20" s="2" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="E20" s="2" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S20" s="14" t="str"/>
+      <x:c r="T20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA20" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB20" s="14" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="21">

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food" sheetId="1" r:id="R62d789eb7c6b4922"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss_debuff" sheetId="2" r:id="Rd861e57848874bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food" sheetId="1" r:id="R2e2fe14061e04bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss_debuff" sheetId="2" r:id="R4f769f028a62496c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1658,7 +1658,9 @@
       <x:c r="G1" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H1"/>
+      <x:c r="H1" t="str">
+        <x:v>*dialogues</x:v>
+      </x:c>
       <x:c r="I1"/>
       <x:c r="J1"/>
       <x:c r="K1"/>
@@ -1702,7 +1704,9 @@
       <x:c r="G2" s="2" t="str">
         <x:v>目标美味值隐藏分修正；加到 TargetScore 指数输入。</x:v>
       </x:c>
-      <x:c r="H2"/>
+      <x:c r="H2" t="str">
+        <x:v>Boss 演出对白；支持多行配置，单场不放回随机。</x:v>
+      </x:c>
       <x:c r="I2"/>
       <x:c r="J2"/>
       <x:c r="K2"/>
@@ -1746,7 +1750,9 @@
       <x:c r="G3" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H3"/>
+      <x:c r="H3" t="str">
+        <x:v>list,string</x:v>
+      </x:c>
       <x:c r="I3"/>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -1785,7 +1791,9 @@
       <x:c r="G4">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="H4"/>
+      <x:c r="H4" t="str">
+        <x:v>我要多吃点</x:v>
+      </x:c>
       <x:c r="I4"/>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -1824,7 +1832,9 @@
       <x:c r="G5">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="H5"/>
+      <x:c r="H5" t="str">
+        <x:v>我要多吃点</x:v>
+      </x:c>
       <x:c r="I5"/>
       <x:c r="J5"/>
       <x:c r="K5"/>
@@ -1863,7 +1873,9 @@
       <x:c r="G6">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="H6"/>
+      <x:c r="H6" t="str">
+        <x:v>我要少吃点</x:v>
+      </x:c>
       <x:c r="I6"/>
       <x:c r="J6"/>
       <x:c r="K6"/>
@@ -1902,7 +1914,9 @@
       <x:c r="G7">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="H7"/>
+      <x:c r="H7" t="str">
+        <x:v>我要少吃点</x:v>
+      </x:c>
       <x:c r="I7"/>
       <x:c r="J7"/>
       <x:c r="K7"/>
@@ -1941,7 +1955,9 @@
       <x:c r="G8">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H8"/>
+      <x:c r="H8" t="str">
+        <x:v>都给我再来一份</x:v>
+      </x:c>
       <x:c r="I8"/>
       <x:c r="J8"/>
       <x:c r="K8"/>
@@ -1980,7 +1996,9 @@
       <x:c r="G9">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H9"/>
+      <x:c r="H9" t="str">
+        <x:v>我不喜欢浪费</x:v>
+      </x:c>
       <x:c r="I9"/>
       <x:c r="J9"/>
       <x:c r="K9"/>
@@ -2019,7 +2037,9 @@
       <x:c r="G10">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H10"/>
+      <x:c r="H10" t="str">
+        <x:v>太花里胡哨了</x:v>
+      </x:c>
       <x:c r="I10"/>
       <x:c r="J10"/>
       <x:c r="K10"/>
@@ -2058,7 +2078,9 @@
       <x:c r="G11">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H11"/>
+      <x:c r="H11" t="str">
+        <x:v>我不喜欢</x:v>
+      </x:c>
       <x:c r="I11"/>
       <x:c r="J11"/>
       <x:c r="K11"/>
@@ -2089,7 +2111,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
-        <x:v>每次出菜 -5 金币</x:v>
+        <x:v>每次上菜 -5 金币</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>1</x:v>
@@ -2175,7 +2197,9 @@
       <x:c r="G14">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H14"/>
+      <x:c r="H14" t="str">
+        <x:v>这几块别放肉。</x:v>
+      </x:c>
       <x:c r="I14"/>
       <x:c r="J14"/>
       <x:c r="K14"/>
@@ -2214,7 +2238,9 @@
       <x:c r="G15">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H15"/>
+      <x:c r="H15" t="str">
+        <x:v>先给我来点这个</x:v>
+      </x:c>
       <x:c r="I15"/>
       <x:c r="J15"/>
       <x:c r="K15"/>
@@ -2292,7 +2318,9 @@
       <x:c r="G17">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H17"/>
+      <x:c r="H17" t="str">
+        <x:v>最后上的，先吃。</x:v>
+      </x:c>
       <x:c r="I17"/>
       <x:c r="J17"/>
       <x:c r="K17"/>
@@ -2331,7 +2359,9 @@
       <x:c r="G18">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H18"/>
+      <x:c r="H18" t="str">
+        <x:v>我先吃一点</x:v>
+      </x:c>
       <x:c r="I18"/>
       <x:c r="J18"/>
       <x:c r="K18"/>
@@ -2409,7 +2439,9 @@
       <x:c r="G20">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="H20"/>
+      <x:c r="H20" t="str">
+        <x:v>就这点够谁吃</x:v>
+      </x:c>
       <x:c r="I20"/>
       <x:c r="J20"/>
       <x:c r="K20"/>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -308,7 +308,7 @@
     <t>霸王餐</t>
   </si>
   <si>
-    <t>每次[context]上菜[/context] [gold]-5 金币[/gold]</t>
+    <t>每次[context]上菜[/context] [gold]-3金币[/gold]</t>
   </si>
   <si>
     <t>debuff_fine_dining</t>

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -1721,7 +1721,7 @@
         <v>41</v>
       </c>
       <c r="H9" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -1741,7 +1741,7 @@
         <v>43</v>
       </c>
       <c r="H10" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -1761,7 +1761,7 @@
         <v>45</v>
       </c>
       <c r="H11" s="2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" s="6" customFormat="1" spans="2:8">
@@ -1780,8 +1780,8 @@
       <c r="G12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="6">
-        <v>0.5</v>
+      <c r="H12" s="2">
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" s="6" customFormat="1" spans="2:8">
@@ -1800,8 +1800,8 @@
       <c r="G13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="6">
-        <v>0.5</v>
+      <c r="H13" s="2">
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="2:8">

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -218,7 +218,8 @@
     <t>放纵餐</t>
   </si>
   <si>
-    <t>获得一行餐桌格</t>
+    <t>获得一行餐桌格
+美味值要求更高</t>
   </si>
   <si>
     <t>我要多吃点</t>
@@ -230,7 +231,8 @@
     <t>暴食餐</t>
   </si>
   <si>
-    <t>获得一列餐桌格</t>
+    <t>获得一列餐桌格
+美味值要求更高</t>
   </si>
   <si>
     <t>debuff_kids_meal</t>
@@ -1000,7 +1002,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1009,6 +1011,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1664,43 +1669,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" spans="2:8">
-      <c r="B7" s="6" t="s">
+    <row r="7" s="7" customFormat="1" spans="2:8">
+      <c r="B7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" spans="2:8">
-      <c r="B8" s="6" t="s">
+    <row r="8" s="7" customFormat="1" spans="2:8">
+      <c r="B8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1764,40 +1769,40 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" spans="2:8">
-      <c r="B12" s="6" t="s">
+    <row r="12" s="7" customFormat="1" spans="2:8">
+      <c r="B12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" spans="2:8">
-      <c r="B13" s="6" t="s">
+    <row r="13" s="7" customFormat="1" spans="2:8">
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="H13" s="2">
@@ -1988,7 +1993,7 @@
       <c r="AA3"/>
       <c r="AB3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:28">
+    <row r="4" s="1" customFormat="1" ht="34" spans="1:28">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>65</v>
@@ -1996,7 +2001,7 @@
       <c r="C4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E4" s="1">
@@ -2029,18 +2034,18 @@
       <c r="AA4"/>
       <c r="AB4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:28">
+    <row r="5" s="1" customFormat="1" ht="34" spans="1:28">
       <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="G5">
@@ -2113,7 +2118,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:28">
       <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2122,7 +2127,7 @@
       <c r="D7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>1</v>
       </c>
       <c r="G7">
@@ -2437,7 +2442,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:28">
       <c r="A15" s="3"/>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2446,7 +2451,7 @@
       <c r="D15" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>1</v>
       </c>
       <c r="G15">
@@ -2523,7 +2528,7 @@
       <c r="C17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>114</v>
       </c>
       <c r="E17" s="2">
@@ -2605,7 +2610,7 @@
       <c r="C19" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>122</v>
       </c>
       <c r="E19" s="2">
@@ -2644,7 +2649,7 @@
       <c r="C20" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>125</v>
       </c>
       <c r="E20" s="2">

--- a/GourmetProject/GameConfig/Datas/food.xlsx
+++ b/GourmetProject/GameConfig/Datas/food.xlsx
@@ -319,7 +319,7 @@
     <t>高级料理</t>
   </si>
   <si>
-    <t>食物基础分减半</t>
+    <t>食物分数减半</t>
   </si>
   <si>
     <t>debuff_vegetarian</t>
